--- a/outputs/tabel/tabel_11_hasil_tuning_hyperparameter_model_gru.xlsx
+++ b/outputs/tabel/tabel_11_hasil_tuning_hyperparameter_model_gru.xlsx
@@ -490,10 +490,10 @@
         <v>7.940313803776057</v>
       </c>
       <c r="G2" t="n">
-        <v>17.03193414700036</v>
+        <v>31.14439085599952</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1703193414700036</v>
+        <v>0.3114439085599952</v>
       </c>
       <c r="I2" t="n">
         <v>671</v>
@@ -522,10 +522,10 @@
         <v>2.797007866528347</v>
       </c>
       <c r="G3" t="n">
-        <v>79.06562707100011</v>
+        <v>153.4534775740003</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1581312541420002</v>
+        <v>0.3069069551480006</v>
       </c>
       <c r="I3" t="n">
         <v>671</v>
@@ -554,10 +554,10 @@
         <v>2.042586701352382</v>
       </c>
       <c r="G4" t="n">
-        <v>158.0103299110001</v>
+        <v>294.485079473</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1580103299110001</v>
+        <v>0.2944850794730001</v>
       </c>
       <c r="I4" t="n">
         <v>671</v>
@@ -586,10 +586,10 @@
         <v>3.096167775428629</v>
       </c>
       <c r="G5" t="n">
-        <v>17.84011972400003</v>
+        <v>31.89331566100009</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1784011972400003</v>
+        <v>0.3189331566100009</v>
       </c>
       <c r="I5" t="n">
         <v>1941</v>
@@ -618,10 +618,10 @@
         <v>2.072343190625749</v>
       </c>
       <c r="G6" t="n">
-        <v>81.11143801099979</v>
+        <v>145.4834245920001</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1622228760219996</v>
+        <v>0.2909668491840002</v>
       </c>
       <c r="I6" t="n">
         <v>1941</v>
@@ -650,10 +650,10 @@
         <v>2.332429893243875</v>
       </c>
       <c r="G7" t="n">
-        <v>161.082147046</v>
+        <v>291.8717473070001</v>
       </c>
       <c r="H7" t="n">
-        <v>0.161082147046</v>
+        <v>0.2918717473070001</v>
       </c>
       <c r="I7" t="n">
         <v>1941</v>
@@ -682,10 +682,10 @@
         <v>3.281196258008131</v>
       </c>
       <c r="G8" t="n">
-        <v>18.1426122429998</v>
+        <v>31.77901835200009</v>
       </c>
       <c r="H8" t="n">
-        <v>0.181426122429998</v>
+        <v>0.3177901835200009</v>
       </c>
       <c r="I8" t="n">
         <v>3811</v>
@@ -714,10 +714,10 @@
         <v>1.979729253590651</v>
       </c>
       <c r="G9" t="n">
-        <v>83.04600583499996</v>
+        <v>150.3899834889999</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1660920116699999</v>
+        <v>0.3007799669779997</v>
       </c>
       <c r="I9" t="n">
         <v>3811</v>
@@ -750,10 +750,10 @@
         <v>3.944333247021107</v>
       </c>
       <c r="G10" t="n">
-        <v>164.0672824480002</v>
+        <v>311.5673191810001</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1640672824480002</v>
+        <v>0.3115673191810001</v>
       </c>
       <c r="I10" t="n">
         <v>3811</v>
@@ -782,10 +782,10 @@
         <v>2.936236073402946</v>
       </c>
       <c r="G11" t="n">
-        <v>18.54659536700001</v>
+        <v>34.25378055999954</v>
       </c>
       <c r="H11" t="n">
-        <v>0.1854659536700001</v>
+        <v>0.3425378055999954</v>
       </c>
       <c r="I11" t="n">
         <v>6281</v>
@@ -814,10 +814,10 @@
         <v>2.365608533560119</v>
       </c>
       <c r="G12" t="n">
-        <v>81.76266566999993</v>
+        <v>153.4025459669992</v>
       </c>
       <c r="H12" t="n">
-        <v>0.1635253313399999</v>
+        <v>0.3068050919339985</v>
       </c>
       <c r="I12" t="n">
         <v>6281</v>
@@ -846,10 +846,10 @@
         <v>2.627875606011886</v>
       </c>
       <c r="G13" t="n">
-        <v>164.7140442960003</v>
+        <v>288.1765002880002</v>
       </c>
       <c r="H13" t="n">
-        <v>0.1647140442960003</v>
+        <v>0.2881765002880002</v>
       </c>
       <c r="I13" t="n">
         <v>6281</v>
@@ -878,10 +878,10 @@
         <v>7.195980945109542</v>
       </c>
       <c r="G14" t="n">
-        <v>18.36716911999974</v>
+        <v>32.7507175210003</v>
       </c>
       <c r="H14" t="n">
-        <v>0.1836716911999974</v>
+        <v>0.3275071752100029</v>
       </c>
       <c r="I14" t="n">
         <v>9351</v>
@@ -910,10 +910,10 @@
         <v>2.309361999001109</v>
       </c>
       <c r="G15" t="n">
-        <v>86.45495442599986</v>
+        <v>157.6379009149996</v>
       </c>
       <c r="H15" t="n">
-        <v>0.1729099088519997</v>
+        <v>0.3152758018299992</v>
       </c>
       <c r="I15" t="n">
         <v>9351</v>
@@ -942,10 +942,10 @@
         <v>2.089105095532841</v>
       </c>
       <c r="G16" t="n">
-        <v>167.4425422909999</v>
+        <v>319.3314337339998</v>
       </c>
       <c r="H16" t="n">
-        <v>0.1674425422909999</v>
+        <v>0.3193314337339998</v>
       </c>
       <c r="I16" t="n">
         <v>9351</v>
